--- a/reports/Debug-snowbowl-20251230/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Day (Actual)_Payroll.xlsx
@@ -14,77 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="258">
   <si>
     <t>eecode</t>
   </si>
   <si>
+    <t>F627</t>
+  </si>
+  <si>
+    <t>E483</t>
+  </si>
+  <si>
+    <t>D954</t>
+  </si>
+  <si>
+    <t>B884</t>
+  </si>
+  <si>
+    <t>A749</t>
+  </si>
+  <si>
+    <t>A4BY</t>
+  </si>
+  <si>
+    <t>G891</t>
+  </si>
+  <si>
+    <t>A1K3</t>
+  </si>
+  <si>
+    <t>I304</t>
+  </si>
+  <si>
     <t>A3ML</t>
   </si>
   <si>
-    <t>F627</t>
+    <t>A337</t>
   </si>
   <si>
     <t>A2CL</t>
   </si>
   <si>
-    <t>A337</t>
+    <t>J405</t>
+  </si>
+  <si>
+    <t>A31F</t>
+  </si>
+  <si>
+    <t>A2C3</t>
+  </si>
+  <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>G693</t>
+  </si>
+  <si>
+    <t>C282</t>
+  </si>
+  <si>
+    <t>D528</t>
+  </si>
+  <si>
+    <t>D521</t>
   </si>
   <si>
     <t>H352</t>
   </si>
   <si>
-    <t>E483</t>
-  </si>
-  <si>
-    <t>G891</t>
-  </si>
-  <si>
-    <t>D954</t>
-  </si>
-  <si>
-    <t>B884</t>
-  </si>
-  <si>
-    <t>A749</t>
-  </si>
-  <si>
-    <t>D521</t>
-  </si>
-  <si>
-    <t>A4BY</t>
-  </si>
-  <si>
-    <t>I304</t>
-  </si>
-  <si>
-    <t>D528</t>
-  </si>
-  <si>
-    <t>A1K3</t>
-  </si>
-  <si>
-    <t>J405</t>
-  </si>
-  <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>G693</t>
-  </si>
-  <si>
-    <t>C282</t>
-  </si>
-  <si>
     <t>D816</t>
   </si>
   <si>
-    <t>A2C3</t>
-  </si>
-  <si>
-    <t>A31F</t>
-  </si>
-  <si>
     <t>B221</t>
   </si>
   <si>
@@ -94,6 +94,9 @@
     <t>I384</t>
   </si>
   <si>
+    <t>A42T</t>
+  </si>
+  <si>
     <t>A3IH</t>
   </si>
   <si>
@@ -103,54 +106,51 @@
     <t>E568</t>
   </si>
   <si>
+    <t>A0QK</t>
+  </si>
+  <si>
+    <t>J561</t>
+  </si>
+  <si>
     <t>A35Y</t>
   </si>
   <si>
-    <t>A0QK</t>
-  </si>
-  <si>
     <t>A3IP</t>
   </si>
   <si>
-    <t>J561</t>
+    <t>A3IC</t>
+  </si>
+  <si>
+    <t>A3KD</t>
+  </si>
+  <si>
+    <t>A3WC</t>
   </si>
   <si>
     <t>A0QH</t>
   </si>
   <si>
-    <t>A3IC</t>
-  </si>
-  <si>
-    <t>A3WC</t>
-  </si>
-  <si>
-    <t>A3KD</t>
-  </si>
-  <si>
-    <t>A42T</t>
-  </si>
-  <si>
     <t>F703</t>
   </si>
   <si>
+    <t>F035</t>
+  </si>
+  <si>
     <t>F497</t>
   </si>
   <si>
-    <t>F035</t>
+    <t>C349</t>
+  </si>
+  <si>
+    <t>B896</t>
+  </si>
+  <si>
+    <t>C215</t>
   </si>
   <si>
     <t>G963</t>
   </si>
   <si>
-    <t>B896</t>
-  </si>
-  <si>
-    <t>C349</t>
-  </si>
-  <si>
-    <t>C215</t>
-  </si>
-  <si>
     <t>B567</t>
   </si>
   <si>
@@ -160,6 +160,18 @@
     <t>E835</t>
   </si>
   <si>
+    <t>E893</t>
+  </si>
+  <si>
+    <t>A3I5</t>
+  </si>
+  <si>
+    <t>G381</t>
+  </si>
+  <si>
+    <t>A382</t>
+  </si>
+  <si>
     <t>E660</t>
   </si>
   <si>
@@ -169,93 +181,81 @@
     <t>F124</t>
   </si>
   <si>
-    <t>A382</t>
+    <t>D619</t>
+  </si>
+  <si>
+    <t>G190</t>
+  </si>
+  <si>
+    <t>A32C</t>
+  </si>
+  <si>
+    <t>A3HX</t>
+  </si>
+  <si>
+    <t>A661</t>
   </si>
   <si>
     <t>G573</t>
   </si>
   <si>
-    <t>E893</t>
-  </si>
-  <si>
-    <t>D619</t>
-  </si>
-  <si>
-    <t>A3I5</t>
-  </si>
-  <si>
-    <t>G381</t>
-  </si>
-  <si>
-    <t>G190</t>
+    <t>H115</t>
   </si>
   <si>
     <t>A170</t>
   </si>
   <si>
-    <t>A32C</t>
-  </si>
-  <si>
     <t>C644</t>
   </si>
   <si>
-    <t>H115</t>
-  </si>
-  <si>
-    <t>A661</t>
-  </si>
-  <si>
-    <t>A3HX</t>
+    <t>A2CR</t>
+  </si>
+  <si>
+    <t>F959</t>
+  </si>
+  <si>
+    <t>J447</t>
+  </si>
+  <si>
+    <t>A3RR</t>
+  </si>
+  <si>
+    <t>A3RQ</t>
+  </si>
+  <si>
+    <t>A2CT</t>
   </si>
   <si>
     <t>A0QI</t>
   </si>
   <si>
-    <t>A3RR</t>
+    <t>A0TR</t>
+  </si>
+  <si>
+    <t>A0ZW</t>
+  </si>
+  <si>
+    <t>A3VD</t>
+  </si>
+  <si>
+    <t>A2FK</t>
+  </si>
+  <si>
+    <t>A4FO</t>
+  </si>
+  <si>
+    <t>A3T9</t>
+  </si>
+  <si>
+    <t>F510</t>
   </si>
   <si>
     <t>A2FB</t>
   </si>
   <si>
-    <t>A4FO</t>
-  </si>
-  <si>
-    <t>A3VD</t>
-  </si>
-  <si>
-    <t>A2CT</t>
-  </si>
-  <si>
-    <t>A0TR</t>
-  </si>
-  <si>
-    <t>F959</t>
-  </si>
-  <si>
-    <t>J447</t>
-  </si>
-  <si>
-    <t>A0ZW</t>
-  </si>
-  <si>
-    <t>F510</t>
-  </si>
-  <si>
-    <t>A2CR</t>
-  </si>
-  <si>
-    <t>A3RQ</t>
-  </si>
-  <si>
-    <t>A2FK</t>
-  </si>
-  <si>
     <t>A3X6</t>
   </si>
   <si>
-    <t>A3T9</t>
-  </si>
-  <si>
     <t>A399</t>
   </si>
   <si>
@@ -268,19 +268,49 @@
     <t>E190</t>
   </si>
   <si>
+    <t>A3II</t>
+  </si>
+  <si>
+    <t>A2YQ</t>
+  </si>
+  <si>
+    <t>H439</t>
+  </si>
+  <si>
+    <t>A2PL</t>
+  </si>
+  <si>
+    <t>A3RK</t>
+  </si>
+  <si>
+    <t>A30J</t>
+  </si>
+  <si>
+    <t>A2JE</t>
+  </si>
+  <si>
     <t>A11F</t>
   </si>
   <si>
     <t>A2I3</t>
   </si>
   <si>
+    <t>A1F9</t>
+  </si>
+  <si>
+    <t>A2BQ</t>
+  </si>
+  <si>
+    <t>A2ID</t>
+  </si>
+  <si>
     <t>A3RO</t>
   </si>
   <si>
     <t>A4FN</t>
   </si>
   <si>
-    <t>A2ID</t>
+    <t>A3O3</t>
   </si>
   <si>
     <t>A46N</t>
@@ -289,97 +319,124 @@
     <t>A3UU</t>
   </si>
   <si>
-    <t>A3RK</t>
-  </si>
-  <si>
-    <t>A1F9</t>
-  </si>
-  <si>
-    <t>A3O3</t>
-  </si>
-  <si>
-    <t>H439</t>
-  </si>
-  <si>
-    <t>A2JE</t>
-  </si>
-  <si>
-    <t>A2BQ</t>
-  </si>
-  <si>
-    <t>A30J</t>
-  </si>
-  <si>
-    <t>A2PL</t>
-  </si>
-  <si>
-    <t>A2YQ</t>
-  </si>
-  <si>
-    <t>A3II</t>
+    <t>A0IF</t>
   </si>
   <si>
     <t>E825</t>
   </si>
   <si>
-    <t>A0IF</t>
-  </si>
-  <si>
     <t>A3KP</t>
   </si>
   <si>
+    <t>A0LC</t>
+  </si>
+  <si>
     <t>A3KA</t>
   </si>
   <si>
     <t>A2LG</t>
   </si>
   <si>
-    <t>A0LC</t>
-  </si>
-  <si>
     <t>A3XF</t>
   </si>
   <si>
     <t>G605</t>
   </si>
   <si>
+    <t>A0H4</t>
+  </si>
+  <si>
+    <t>I588</t>
+  </si>
+  <si>
+    <t>A3YJ</t>
+  </si>
+  <si>
+    <t>A41F</t>
+  </si>
+  <si>
     <t>A3KG</t>
   </si>
   <si>
+    <t>A3J4</t>
+  </si>
+  <si>
+    <t>A3YI</t>
+  </si>
+  <si>
+    <t>A41H</t>
+  </si>
+  <si>
+    <t>A0TT</t>
+  </si>
+  <si>
     <t>E794</t>
   </si>
   <si>
     <t>A3JQ</t>
   </si>
   <si>
-    <t>A0H4</t>
-  </si>
-  <si>
-    <t>A3YJ</t>
-  </si>
-  <si>
-    <t>A3YI</t>
-  </si>
-  <si>
-    <t>A41H</t>
-  </si>
-  <si>
-    <t>A0TT</t>
-  </si>
-  <si>
-    <t>I588</t>
-  </si>
-  <si>
-    <t>A3J4</t>
-  </si>
-  <si>
-    <t>A41F</t>
+    <t>A3UE</t>
+  </si>
+  <si>
+    <t>A3YX</t>
+  </si>
+  <si>
+    <t>A3YQ</t>
+  </si>
+  <si>
+    <t>A1H9</t>
   </si>
   <si>
     <t>A45O</t>
   </si>
   <si>
-    <t>A1H9</t>
+    <t>C913</t>
+  </si>
+  <si>
+    <t>H636</t>
+  </si>
+  <si>
+    <t>A3TS</t>
+  </si>
+  <si>
+    <t>A3GV</t>
+  </si>
+  <si>
+    <t>C926</t>
+  </si>
+  <si>
+    <t>A3I6</t>
+  </si>
+  <si>
+    <t>A3Z8</t>
+  </si>
+  <si>
+    <t>A3TQ</t>
+  </si>
+  <si>
+    <t>A0GJ</t>
+  </si>
+  <si>
+    <t>A2KF</t>
+  </si>
+  <si>
+    <t>A3TO</t>
+  </si>
+  <si>
+    <t>B2UZ</t>
+  </si>
+  <si>
+    <t>A0VA</t>
+  </si>
+  <si>
+    <t>A3Z0</t>
+  </si>
+  <si>
+    <t>A3ZC</t>
+  </si>
+  <si>
+    <t>A48R</t>
   </si>
   <si>
     <t>A4DP</t>
@@ -388,91 +445,37 @@
     <t>A3Z3</t>
   </si>
   <si>
-    <t>A3ZC</t>
-  </si>
-  <si>
-    <t>A0VA</t>
-  </si>
-  <si>
-    <t>H636</t>
-  </si>
-  <si>
-    <t>C913</t>
-  </si>
-  <si>
-    <t>A48R</t>
-  </si>
-  <si>
-    <t>A3GV</t>
-  </si>
-  <si>
-    <t>A3TS</t>
-  </si>
-  <si>
-    <t>A3I6</t>
-  </si>
-  <si>
-    <t>B2UZ</t>
-  </si>
-  <si>
-    <t>A3YQ</t>
-  </si>
-  <si>
-    <t>A3YX</t>
-  </si>
-  <si>
-    <t>A3TO</t>
-  </si>
-  <si>
-    <t>A3UE</t>
-  </si>
-  <si>
-    <t>C926</t>
-  </si>
-  <si>
-    <t>A3Z0</t>
-  </si>
-  <si>
-    <t>A3TQ</t>
-  </si>
-  <si>
-    <t>A0GJ</t>
-  </si>
-  <si>
-    <t>A3Z8</t>
-  </si>
-  <si>
-    <t>A2KF</t>
-  </si>
-  <si>
     <t>C213</t>
   </si>
   <si>
     <t>A04U</t>
   </si>
   <si>
+    <t>A4DU</t>
+  </si>
+  <si>
+    <t>A3UH</t>
+  </si>
+  <si>
+    <t>A4AX</t>
+  </si>
+  <si>
+    <t>A3Z2</t>
+  </si>
+  <si>
+    <t>A515</t>
+  </si>
+  <si>
     <t>A3YU</t>
   </si>
   <si>
-    <t>A515</t>
-  </si>
-  <si>
-    <t>A3UH</t>
-  </si>
-  <si>
-    <t>A4DU</t>
-  </si>
-  <si>
-    <t>A3Z2</t>
-  </si>
-  <si>
-    <t>A4AX</t>
+    <t>A2HX</t>
   </si>
   <si>
     <t>A04Q</t>
   </si>
   <si>
-    <t>A2HX</t>
+    <t>A4CZ</t>
   </si>
   <si>
     <t>A0J5</t>
@@ -481,106 +484,103 @@
     <t>A194</t>
   </si>
   <si>
-    <t>A4CZ</t>
+    <t>A4AF</t>
+  </si>
+  <si>
+    <t>F025</t>
+  </si>
+  <si>
+    <t>A37Y</t>
+  </si>
+  <si>
+    <t>A2WI</t>
+  </si>
+  <si>
+    <t>A4AL</t>
   </si>
   <si>
     <t>A4CF</t>
   </si>
   <si>
-    <t>F025</t>
-  </si>
-  <si>
-    <t>A37Y</t>
-  </si>
-  <si>
-    <t>A2WI</t>
-  </si>
-  <si>
-    <t>A4AL</t>
-  </si>
-  <si>
     <t>A34P</t>
   </si>
   <si>
-    <t>A4AF</t>
-  </si>
-  <si>
     <t>B035</t>
   </si>
   <si>
     <t>A39M</t>
   </si>
   <si>
+    <t>A3ON</t>
+  </si>
+  <si>
+    <t>A3PS</t>
+  </si>
+  <si>
+    <t>B322</t>
+  </si>
+  <si>
+    <t>A3S7</t>
+  </si>
+  <si>
+    <t>C947</t>
+  </si>
+  <si>
     <t>A2GD</t>
   </si>
   <si>
-    <t>C947</t>
-  </si>
-  <si>
-    <t>A3S7</t>
-  </si>
-  <si>
-    <t>B322</t>
-  </si>
-  <si>
-    <t>A3PS</t>
-  </si>
-  <si>
-    <t>A3ON</t>
+    <t>H146</t>
+  </si>
+  <si>
+    <t>G531</t>
+  </si>
+  <si>
+    <t>D754</t>
+  </si>
+  <si>
+    <t>A3O6</t>
   </si>
   <si>
     <t>A0IJ</t>
   </si>
   <si>
-    <t>D754</t>
-  </si>
-  <si>
-    <t>G531</t>
-  </si>
-  <si>
-    <t>A3O6</t>
-  </si>
-  <si>
-    <t>H146</t>
-  </si>
-  <si>
     <t>G448</t>
   </si>
   <si>
+    <t>A2PQ</t>
+  </si>
+  <si>
+    <t>A2R6</t>
+  </si>
+  <si>
+    <t>A3TW</t>
+  </si>
+  <si>
+    <t>A3TX</t>
+  </si>
+  <si>
     <t>A3TY</t>
   </si>
   <si>
-    <t>A3TW</t>
-  </si>
-  <si>
-    <t>A2PQ</t>
-  </si>
-  <si>
-    <t>A3TX</t>
-  </si>
-  <si>
-    <t>A2R6</t>
+    <t>A415</t>
   </si>
   <si>
     <t>D667</t>
   </si>
   <si>
-    <t>A415</t>
-  </si>
-  <si>
     <t>A3DQ</t>
   </si>
   <si>
+    <t>A2ST</t>
+  </si>
+  <si>
     <t>A393</t>
   </si>
   <si>
-    <t>A2ST</t>
+    <t>D575</t>
   </si>
   <si>
     <t>A3MB</t>
-  </si>
-  <si>
-    <t>D575</t>
   </si>
   <si>
     <t>start_punchtime</t>
@@ -1201,22 +1201,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46021.3244675926</v>
+        <v>46021.33077546296</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="2">
-        <v>46021.68181712963</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>197</v>
       </c>
       <c r="G2" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1233,18 +1229,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46021.33077546296</v>
+        <v>46021.32575231481</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="2">
+        <v>46021.6834375</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F3" s="2" t="s">
         <v>197</v>
       </c>
       <c r="G3" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46021.32745370371</v>
+        <v>46021.33295138889</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D4" s="2">
-        <v>46021.68949074074</v>
+        <v>46021.70287037037</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>195</v>
@@ -1276,7 +1276,7 @@
         <v>197</v>
       </c>
       <c r="G4" s="2">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1293,13 +1293,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46021.33247685185</v>
+        <v>46021.33149305556</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D5" s="2">
-        <v>46021.70076388889</v>
+        <v>46021.70489583333</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>195</v>
@@ -1308,7 +1308,7 @@
         <v>197</v>
       </c>
       <c r="G5" s="2">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1325,13 +1325,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46021.32677083334</v>
+        <v>46021.33415509259</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D6" s="2">
-        <v>46021.70348379629</v>
+        <v>46021.34268518518</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>195</v>
@@ -1340,7 +1340,7 @@
         <v>197</v>
       </c>
       <c r="G6" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1357,13 +1357,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>46021.32575231481</v>
+        <v>46021.33662037037</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D7" s="2">
-        <v>46021.6834375</v>
+        <v>46021.68881944445</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>195</v>
@@ -1421,13 +1421,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>46021.33295138889</v>
+        <v>46021.32769675926</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D9" s="2">
-        <v>46021.70287037037</v>
+        <v>46021.69712962963</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>195</v>
@@ -1436,7 +1436,7 @@
         <v>197</v>
       </c>
       <c r="G9" s="2">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46021.33149305556</v>
+        <v>46021.32430555556</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D10" s="2">
-        <v>46021.70489583333</v>
+        <v>46021.72810185186</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>195</v>
@@ -1468,7 +1468,7 @@
         <v>197</v>
       </c>
       <c r="G10" s="2">
-        <v>18.7</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -1485,13 +1485,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>46021.33415509259</v>
+        <v>46021.3244675926</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D11" s="2">
-        <v>46021.34268518518</v>
+        <v>46021.68181712963</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>195</v>
@@ -1517,13 +1517,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46021.32498842593</v>
+        <v>46021.33247685185</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D12" s="2">
-        <v>46021.70180555555</v>
+        <v>46021.70076388889</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>195</v>
@@ -1532,7 +1532,7 @@
         <v>197</v>
       </c>
       <c r="G12" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1549,13 +1549,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46021.33662037037</v>
+        <v>46021.32745370371</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D13" s="2">
-        <v>46021.68881944445</v>
+        <v>46021.68949074074</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>195</v>
@@ -1564,7 +1564,7 @@
         <v>197</v>
       </c>
       <c r="G13" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>
@@ -1581,13 +1581,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>46021.32430555556</v>
+        <v>46021.33856481482</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D14" s="2">
-        <v>46021.72810185186</v>
+        <v>46021.70614583333</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>195</v>
@@ -1596,7 +1596,7 @@
         <v>197</v>
       </c>
       <c r="G14" s="2">
-        <v>23</v>
+        <v>18.7</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46021.32336805556</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D15" s="2">
-        <v>46021.70552083333</v>
+        <v>46021.69890046296</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>195</v>
@@ -1628,7 +1628,7 @@
         <v>197</v>
       </c>
       <c r="G15" s="2">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -1645,13 +1645,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46021.32769675926</v>
+        <v>46021.33353009259</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D16" s="2">
-        <v>46021.69712962963</v>
+        <v>46021.70708333333</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>195</v>
@@ -1660,7 +1660,7 @@
         <v>197</v>
       </c>
       <c r="G16" s="2">
-        <v>18.6</v>
+        <v>19.25</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
@@ -1677,13 +1677,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46021.33856481482</v>
+        <v>46021.32285879629</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D17" s="2">
-        <v>46021.70614583333</v>
+        <v>46021.73335648148</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>195</v>
@@ -1692,7 +1692,7 @@
         <v>197</v>
       </c>
       <c r="G17" s="2">
-        <v>18.7</v>
+        <v>26.8</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -1709,13 +1709,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>46021.32285879629</v>
+        <v>46021.34115740741</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D18" s="2">
-        <v>46021.73335648148</v>
+        <v>46021.70405092592</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>195</v>
@@ -1724,7 +1724,7 @@
         <v>197</v>
       </c>
       <c r="G18" s="2">
-        <v>26.8</v>
+        <v>18.35</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1741,13 +1741,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46021.34115740741</v>
+        <v>46021.32355324074</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D19" s="2">
-        <v>46021.70405092592</v>
+        <v>46021.70134259259</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>195</v>
@@ -1756,7 +1756,7 @@
         <v>197</v>
       </c>
       <c r="G19" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>46021.32355324074</v>
+        <v>46021.32336805556</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D20" s="2">
-        <v>46021.70134259259</v>
+        <v>46021.70552083333</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>195</v>
@@ -1805,13 +1805,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46021.33861111111</v>
+        <v>46021.32498842593</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D21" s="2">
-        <v>46021.68800925926</v>
+        <v>46021.70180555555</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>195</v>
@@ -1820,7 +1820,7 @@
         <v>197</v>
       </c>
       <c r="G21" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -1837,13 +1837,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46021.33353009259</v>
+        <v>46021.32677083334</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D22" s="2">
-        <v>46021.70708333333</v>
+        <v>46021.70348379629</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>195</v>
@@ -1852,7 +1852,7 @@
         <v>197</v>
       </c>
       <c r="G22" s="2">
-        <v>19.25</v>
+        <v>18.7</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -1869,13 +1869,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.33861111111</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D23" s="2">
-        <v>46021.69890046296</v>
+        <v>46021.68800925926</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>195</v>
@@ -1884,7 +1884,7 @@
         <v>197</v>
       </c>
       <c r="G23" s="2">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46021.49797453704</v>
+        <v>46021.00009259259</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D27" s="2">
-        <v>46022.00203703704</v>
+        <v>46021.25017361111</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>195</v>
@@ -2029,13 +2029,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>46021.49394675926</v>
+        <v>46021.49797453704</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D28" s="2">
-        <v>46022.00222222223</v>
+        <v>46022.00203703704</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>195</v>
@@ -2061,13 +2061,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>46021.32273148148</v>
+        <v>46021.49394675926</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D29" s="2">
-        <v>46021.72858796296</v>
+        <v>46022.00222222223</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>195</v>
@@ -2076,7 +2076,7 @@
         <v>199</v>
       </c>
       <c r="G29" s="2">
-        <v>30.75</v>
+        <v>20.2</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
@@ -2093,13 +2093,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>46021.00030092592</v>
+        <v>46021.32273148148</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D30" s="2">
-        <v>46021.50903935185</v>
+        <v>46021.72858796296</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>195</v>
@@ -2108,7 +2108,7 @@
         <v>199</v>
       </c>
       <c r="G30" s="2">
-        <v>19.65</v>
+        <v>30.75</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2157,18 +2157,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>46021.98780092593</v>
+        <v>46021.49717592593</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="D32" s="2">
+        <v>46022.01121527778</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F32" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G32" s="2">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -2185,13 +2189,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>46021.49717592593</v>
+        <v>46021.00030092592</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D33" s="2">
-        <v>46022.01121527778</v>
+        <v>46021.50903935185</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>195</v>
@@ -2200,7 +2204,7 @@
         <v>199</v>
       </c>
       <c r="G33" s="2">
-        <v>22.4</v>
+        <v>19.65</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2217,7 +2221,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>46021.48512731482</v>
+        <v>46021.98780092593</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>191</v>
@@ -2277,13 +2281,17 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>46021.99130787037</v>
+        <v>46021.53125</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="D36" s="2">
+        <v>46021.92871527778</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F36" s="2" t="s">
         <v>199</v>
       </c>
@@ -2305,17 +2313,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>46021.53125</v>
+        <v>46021.99130787037</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="2">
-        <v>46021.92871527778</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
         <v>199</v>
       </c>
@@ -2337,22 +2341,18 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46021.00009259259</v>
+        <v>46021.48512731482</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="2">
-        <v>46021.25017361111</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
         <v>199</v>
       </c>
       <c r="G38" s="2">
-        <v>20.2</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -2401,13 +2401,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>46021.07305555556</v>
+        <v>46021.30290509259</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D40" s="2">
-        <v>46021.40865740741</v>
+        <v>46021.7384375</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>195</v>
@@ -2416,7 +2416,7 @@
         <v>200</v>
       </c>
       <c r="G40" s="2">
-        <v>23</v>
+        <v>18.35</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46021.30290509259</v>
+        <v>46021.07305555556</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D41" s="2">
-        <v>46021.7384375</v>
+        <v>46021.40865740741</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>195</v>
@@ -2448,7 +2448,7 @@
         <v>200</v>
       </c>
       <c r="G41" s="2">
-        <v>18.35</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2465,18 +2465,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46021.69020833333</v>
+        <v>46021.68973379629</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="D42" s="2">
+        <v>46022.05234953704</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F42" s="2" t="s">
         <v>201</v>
       </c>
       <c r="G42" s="2">
-        <v>23</v>
+        <v>29.25</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2521,13 +2525,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>46021.68973379629</v>
+        <v>46021.07203703704</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D44" s="2">
-        <v>46022.05234953704</v>
+        <v>46021.40556712963</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>195</v>
@@ -2536,7 +2540,7 @@
         <v>201</v>
       </c>
       <c r="G44" s="2">
-        <v>29.25</v>
+        <v>22.4</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -2553,22 +2557,18 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>46021.07203703704</v>
+        <v>46021.69020833333</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="2">
-        <v>46021.40556712963</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
         <v>201</v>
       </c>
       <c r="G45" s="2">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2585,13 +2585,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>46021.35474537037</v>
+        <v>46021.52267361111</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D46" s="2">
-        <v>46021.50049768519</v>
+        <v>46021.67354166666</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>195</v>
@@ -2617,13 +2617,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>46021.52267361111</v>
+        <v>46021.35474537037</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D47" s="2">
-        <v>46021.67354166666</v>
+        <v>46021.50049768519</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>195</v>
@@ -2713,13 +2713,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>46021.32228009259</v>
+        <v>46021.32982638889</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D50" s="2">
-        <v>46021.73648148148</v>
+        <v>46021.70662037037</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>195</v>
@@ -2728,7 +2728,7 @@
         <v>203</v>
       </c>
       <c r="G50" s="2">
-        <v>20.95</v>
+        <v>22.4</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2745,13 +2745,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>46021.32166666666</v>
+        <v>46021.31821759259</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D51" s="2">
-        <v>46021.75599537037</v>
+        <v>46021.7362037037</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>195</v>
@@ -2760,7 +2760,7 @@
         <v>203</v>
       </c>
       <c r="G51" s="2">
-        <v>19.6</v>
+        <v>19.25</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2777,13 +2777,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>46021.31385416666</v>
+        <v>46021.31978009259</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D52" s="2">
-        <v>46021.72300925926</v>
+        <v>46021.74443287037</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>195</v>
@@ -2792,7 +2792,7 @@
         <v>203</v>
       </c>
       <c r="G52" s="2">
-        <v>22.4</v>
+        <v>23.35</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2841,13 +2841,13 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>46021.3171412037</v>
+        <v>46021.32228009259</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D54" s="2">
-        <v>46021.75480324074</v>
+        <v>46021.73648148148</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>195</v>
@@ -2856,7 +2856,7 @@
         <v>203</v>
       </c>
       <c r="G54" s="2">
-        <v>24.45</v>
+        <v>20.95</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2873,13 +2873,13 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>46021.32982638889</v>
+        <v>46021.32166666666</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D55" s="2">
-        <v>46021.70662037037</v>
+        <v>46021.75599537037</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>195</v>
@@ -2888,7 +2888,7 @@
         <v>203</v>
       </c>
       <c r="G55" s="2">
-        <v>22.4</v>
+        <v>19.6</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2905,13 +2905,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>46021.31793981481</v>
+        <v>46021.31385416666</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D56" s="2">
-        <v>46021.74293981482</v>
+        <v>46021.72300925926</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>195</v>
@@ -2920,7 +2920,7 @@
         <v>203</v>
       </c>
       <c r="G56" s="2">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2937,13 +2937,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>46021.31821759259</v>
+        <v>46021.31793981481</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D57" s="2">
-        <v>46021.7362037037</v>
+        <v>46021.74293981482</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>195</v>
@@ -2952,7 +2952,7 @@
         <v>203</v>
       </c>
       <c r="G57" s="2">
-        <v>19.25</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>46021.31978009259</v>
+        <v>46021.41666666666</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D58" s="2">
-        <v>46021.74443287037</v>
+        <v>46021.68337962963</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>195</v>
@@ -2984,7 +2984,7 @@
         <v>203</v>
       </c>
       <c r="G58" s="2">
-        <v>23.35</v>
+        <v>24.8</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -3001,13 +3001,13 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>46021.41666666666</v>
+        <v>46021.31336805555</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D59" s="2">
-        <v>46021.68337962963</v>
+        <v>46021.71479166667</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>195</v>
@@ -3016,7 +3016,7 @@
         <v>203</v>
       </c>
       <c r="G59" s="2">
-        <v>24.8</v>
+        <v>19.6</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3033,13 +3033,13 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>46021.31928240741</v>
+        <v>46021.31283564815</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D60" s="2">
-        <v>46021.72253472222</v>
+        <v>46021.71603009259</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>195</v>
@@ -3048,7 +3048,7 @@
         <v>203</v>
       </c>
       <c r="G60" s="2">
-        <v>20.2</v>
+        <v>18.75</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>46021.31336805555</v>
+        <v>46021.31502314815</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D61" s="2">
-        <v>46021.71479166667</v>
+        <v>46021.74859953704</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>195</v>
@@ -3080,7 +3080,7 @@
         <v>203</v>
       </c>
       <c r="G61" s="2">
-        <v>19.6</v>
+        <v>25</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -3097,13 +3097,13 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>46021.31967592592</v>
+        <v>46021.3171412037</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D62" s="2">
-        <v>46021.74001157407</v>
+        <v>46021.75480324074</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>195</v>
@@ -3112,7 +3112,7 @@
         <v>203</v>
       </c>
       <c r="G62" s="2">
-        <v>23.35</v>
+        <v>24.45</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -3161,13 +3161,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>46021.31502314815</v>
+        <v>46021.31928240741</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D64" s="2">
-        <v>46021.74859953704</v>
+        <v>46021.72253472222</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>195</v>
@@ -3176,7 +3176,7 @@
         <v>203</v>
       </c>
       <c r="G64" s="2">
-        <v>25</v>
+        <v>20.2</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -3193,13 +3193,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>46021.31283564815</v>
+        <v>46021.31967592592</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D65" s="2">
-        <v>46021.71603009259</v>
+        <v>46021.74001157407</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>195</v>
@@ -3208,7 +3208,7 @@
         <v>203</v>
       </c>
       <c r="G65" s="2">
-        <v>18.75</v>
+        <v>23.35</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3225,13 +3225,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>46021.40486111111</v>
+        <v>46021.30302083334</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D66" s="2">
-        <v>46021.66666666666</v>
+        <v>46021.74266203704</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>195</v>
@@ -3240,7 +3240,7 @@
         <v>204</v>
       </c>
       <c r="G66" s="2">
-        <v>19.75</v>
+        <v>22.4</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
@@ -3257,13 +3257,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>46021.30284722222</v>
+        <v>46021.29760416667</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D67" s="2">
-        <v>46021.53158564815</v>
+        <v>46021.66974537037</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>195</v>
@@ -3272,7 +3272,7 @@
         <v>204</v>
       </c>
       <c r="G67" s="2">
-        <v>19.25</v>
+        <v>19.75</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3289,13 +3289,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>46021.29755787037</v>
+        <v>46021.34483796296</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D68" s="2">
-        <v>46021.61045138889</v>
+        <v>46021.52200231481</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>195</v>
@@ -3304,7 +3304,7 @@
         <v>204</v>
       </c>
       <c r="G68" s="2">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>46021.30393518518</v>
+        <v>46021.30284722222</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D69" s="2">
-        <v>46021.61788194445</v>
+        <v>46021.53158564815</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>195</v>
@@ -3336,7 +3336,7 @@
         <v>204</v>
       </c>
       <c r="G69" s="2">
-        <v>19.35</v>
+        <v>19.25</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3353,13 +3353,13 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>46021.30033564815</v>
+        <v>46021.40924768519</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D70" s="2">
-        <v>46021.49231481482</v>
+        <v>46021.62113425926</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>195</v>
@@ -3417,13 +3417,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>46021.30341435185</v>
+        <v>46021.40486111111</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D72" s="2">
-        <v>46021.6937962963</v>
+        <v>46021.66666666666</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>195</v>
@@ -3432,7 +3432,7 @@
         <v>204</v>
       </c>
       <c r="G72" s="2">
-        <v>19.6</v>
+        <v>19.75</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>46021.29760416667</v>
+        <v>46021.30341435185</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D73" s="2">
-        <v>46021.66974537037</v>
+        <v>46021.6937962963</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>195</v>
@@ -3464,7 +3464,7 @@
         <v>204</v>
       </c>
       <c r="G73" s="2">
-        <v>19.75</v>
+        <v>19.6</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3481,22 +3481,18 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>46021.34483796296</v>
+        <v>46021.3071412037</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D74" s="2">
-        <v>46021.52200231481</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
         <v>204</v>
       </c>
       <c r="G74" s="2">
-        <v>18.6</v>
+        <v>18.75</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
@@ -3513,18 +3509,22 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>46021.3071412037</v>
+        <v>46021.30033564815</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+      <c r="D75" s="2">
+        <v>46021.49231481482</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F75" s="2" t="s">
         <v>204</v>
       </c>
       <c r="G75" s="2">
-        <v>18.75</v>
+        <v>19.25</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>46021.29464120371</v>
+        <v>46021.30064814815</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D76" s="2">
-        <v>46021.70753472222</v>
+        <v>46021.66930555556</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>195</v>
@@ -3556,7 +3556,7 @@
         <v>204</v>
       </c>
       <c r="G76" s="2">
-        <v>22.75</v>
+        <v>19.6</v>
       </c>
       <c r="H76" s="2">
         <v>0</v>
@@ -3573,13 +3573,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>46021.30302083334</v>
+        <v>46021.30393518518</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D77" s="2">
-        <v>46021.74266203704</v>
+        <v>46021.61788194445</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>195</v>
@@ -3588,7 +3588,7 @@
         <v>204</v>
       </c>
       <c r="G77" s="2">
-        <v>22.4</v>
+        <v>19.35</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3605,13 +3605,13 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>46021.40924768519</v>
+        <v>46021.29497685185</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D78" s="2">
-        <v>46021.62113425926</v>
+        <v>46021.52920138889</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>195</v>
@@ -3637,13 +3637,13 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>46021.30064814815</v>
+        <v>46021.29464120371</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D79" s="2">
-        <v>46021.66930555556</v>
+        <v>46021.70753472222</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>195</v>
@@ -3652,7 +3652,7 @@
         <v>204</v>
       </c>
       <c r="G79" s="2">
-        <v>19.6</v>
+        <v>22.75</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3669,13 +3669,13 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>46021.30704861111</v>
+        <v>46021.29755787037</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D80" s="2">
-        <v>46021.66810185185</v>
+        <v>46021.61045138889</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>195</v>
@@ -3684,7 +3684,7 @@
         <v>204</v>
       </c>
       <c r="G80" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3701,13 +3701,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="2">
-        <v>46021.29497685185</v>
+        <v>46021.30704861111</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D81" s="2">
-        <v>46021.52920138889</v>
+        <v>46021.66810185185</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>195</v>
@@ -3861,13 +3861,13 @@
         <v>84</v>
       </c>
       <c r="B86" s="2">
-        <v>46021.30166666667</v>
+        <v>46021.30255787037</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D86" s="2">
-        <v>46021.71854166667</v>
+        <v>46021.54674768518</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>195</v>
@@ -3876,7 +3876,7 @@
         <v>206</v>
       </c>
       <c r="G86" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>85</v>
       </c>
       <c r="B87" s="2">
-        <v>46021.3017824074</v>
+        <v>46021.52453703704</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D87" s="2">
-        <v>46021.56452546296</v>
+        <v>46021.71837962963</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>195</v>
@@ -3908,7 +3908,7 @@
         <v>206</v>
       </c>
       <c r="G87" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>85</v>
       </c>
       <c r="B88" s="2">
-        <v>46021.57658564814</v>
+        <v>46021.30405092592</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D88" s="2">
-        <v>46021.71842592592</v>
+        <v>46021.50297453703</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>195</v>
@@ -3940,7 +3940,7 @@
         <v>206</v>
       </c>
       <c r="G88" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -3957,13 +3957,13 @@
         <v>86</v>
       </c>
       <c r="B89" s="2">
-        <v>46021.30329861111</v>
+        <v>46021.31924768518</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D89" s="2">
-        <v>46021.53689814815</v>
+        <v>46021.50954861111</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>195</v>
@@ -3972,7 +3972,7 @@
         <v>206</v>
       </c>
       <c r="G89" s="2">
-        <v>18.35</v>
+        <v>19.75</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -3989,13 +3989,13 @@
         <v>87</v>
       </c>
       <c r="B90" s="2">
-        <v>46021.29760416667</v>
+        <v>46021.5975</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D90" s="2">
-        <v>46021.59293981481</v>
+        <v>46021.71859953704</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>195</v>
@@ -4004,7 +4004,7 @@
         <v>206</v>
       </c>
       <c r="G90" s="2">
-        <v>19.25</v>
+        <v>18.6</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -4018,16 +4018,16 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B91" s="2">
-        <v>46021.30148148148</v>
+        <v>46021.5621875</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D91" s="2">
-        <v>46021.57016203704</v>
+        <v>46021.71854166667</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>195</v>
@@ -4036,7 +4036,7 @@
         <v>206</v>
       </c>
       <c r="G91" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4050,16 +4050,16 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B92" s="2">
-        <v>46021.58563657408</v>
+        <v>46021.57987268519</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D92" s="2">
-        <v>46021.71880787037</v>
+        <v>46021.71850694445</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>195</v>
@@ -4068,7 +4068,7 @@
         <v>206</v>
       </c>
       <c r="G92" s="2">
-        <v>18.6</v>
+        <v>19.75</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4082,16 +4082,16 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B93" s="2">
-        <v>46021.30381944445</v>
+        <v>46021.546875</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D93" s="2">
-        <v>46021.59515046296</v>
+        <v>46021.72003472222</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>195</v>
@@ -4114,16 +4114,16 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B94" s="2">
-        <v>46021.55568287037</v>
+        <v>46021.30694444444</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D94" s="2">
-        <v>46021.71855324074</v>
+        <v>46021.55842592593</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>195</v>
@@ -4132,7 +4132,7 @@
         <v>206</v>
       </c>
       <c r="G94" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4146,16 +4146,16 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B95" s="2">
-        <v>46021.52431712963</v>
+        <v>46021.71859953704</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D95" s="2">
-        <v>46021.71839120371</v>
+        <v>46021.71865740741</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>195</v>
@@ -4164,7 +4164,7 @@
         <v>206</v>
       </c>
       <c r="G95" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4178,16 +4178,16 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B96" s="2">
-        <v>46021.30387731481</v>
+        <v>46021.30880787037</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D96" s="2">
-        <v>46021.53256944445</v>
+        <v>46021.53739583334</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>195</v>
@@ -4196,7 +4196,7 @@
         <v>206</v>
       </c>
       <c r="G96" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4210,16 +4210,16 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B97" s="2">
-        <v>46021.58520833333</v>
+        <v>46021.60690972222</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D97" s="2">
-        <v>46021.71974537037</v>
+        <v>46021.71853009259</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>195</v>
@@ -4228,7 +4228,7 @@
         <v>206</v>
       </c>
       <c r="G97" s="2">
-        <v>17.85</v>
+        <v>18.6</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
@@ -4242,16 +4242,16 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B98" s="2">
-        <v>46021.30344907408</v>
+        <v>46021.30387731481</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D98" s="2">
-        <v>46021.71900462963</v>
+        <v>46021.53256944445</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>195</v>
@@ -4274,16 +4274,16 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B99" s="2">
-        <v>46021.57987268519</v>
+        <v>46021.30166666667</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D99" s="2">
-        <v>46021.71850694445</v>
+        <v>46021.71854166667</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>195</v>
@@ -4292,7 +4292,7 @@
         <v>206</v>
       </c>
       <c r="G99" s="2">
-        <v>19.75</v>
+        <v>18.7</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4306,16 +4306,16 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B100" s="2">
-        <v>46021.30880787037</v>
+        <v>46021.3017824074</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D100" s="2">
-        <v>46021.53739583334</v>
+        <v>46021.56452546296</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
@@ -4324,7 +4324,7 @@
         <v>206</v>
       </c>
       <c r="G100" s="2">
-        <v>18.6</v>
+        <v>19.25</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
@@ -4338,16 +4338,16 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B101" s="2">
-        <v>46021.30173611111</v>
+        <v>46021.57658564814</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D101" s="2">
-        <v>46021.71909722222</v>
+        <v>46021.71842592592</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>195</v>
@@ -4356,7 +4356,7 @@
         <v>206</v>
       </c>
       <c r="G101" s="2">
-        <v>22.4</v>
+        <v>19.25</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4370,16 +4370,16 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B102" s="2">
-        <v>46021.30694444444</v>
+        <v>46021.30517361111</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D102" s="2">
-        <v>46021.55842592593</v>
+        <v>46021.56539351852</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>195</v>
@@ -4388,7 +4388,7 @@
         <v>206</v>
       </c>
       <c r="G102" s="2">
-        <v>18.6</v>
+        <v>17.85</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
@@ -4402,16 +4402,16 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B103" s="2">
-        <v>46021.71859953704</v>
+        <v>46021.58520833333</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D103" s="2">
-        <v>46021.71865740741</v>
+        <v>46021.71974537037</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>195</v>
@@ -4420,7 +4420,7 @@
         <v>206</v>
       </c>
       <c r="G103" s="2">
-        <v>18.6</v>
+        <v>17.85</v>
       </c>
       <c r="H103" s="2">
         <v>0</v>
@@ -4434,16 +4434,16 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B104" s="2">
-        <v>46021.30069444444</v>
+        <v>46021.30851851852</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D104" s="2">
-        <v>46021.51075231482</v>
+        <v>46021.5903587963</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>195</v>
@@ -4452,7 +4452,7 @@
         <v>206</v>
       </c>
       <c r="G104" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H104" s="2">
         <v>0</v>
@@ -4466,16 +4466,16 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B105" s="2">
-        <v>46021.5975</v>
+        <v>46021.30173611111</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D105" s="2">
-        <v>46021.71859953704</v>
+        <v>46021.71909722222</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>195</v>
@@ -4484,7 +4484,7 @@
         <v>206</v>
       </c>
       <c r="G105" s="2">
-        <v>18.6</v>
+        <v>22.4</v>
       </c>
       <c r="H105" s="2">
         <v>0</v>
@@ -4498,16 +4498,16 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B106" s="2">
-        <v>46021.30851851852</v>
+        <v>46021.30148148148</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D106" s="2">
-        <v>46021.5903587963</v>
+        <v>46021.57016203704</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>195</v>
@@ -4530,16 +4530,16 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B107" s="2">
-        <v>46021.30405092592</v>
+        <v>46021.58563657408</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D107" s="2">
-        <v>46021.50297453703</v>
+        <v>46021.71880787037</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>195</v>
@@ -4548,7 +4548,7 @@
         <v>206</v>
       </c>
       <c r="G107" s="2">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
@@ -4562,16 +4562,16 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B108" s="2">
-        <v>46021.52453703704</v>
+        <v>46021.30329861111</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D108" s="2">
-        <v>46021.71837962963</v>
+        <v>46021.53689814815</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>195</v>
@@ -4580,7 +4580,7 @@
         <v>206</v>
       </c>
       <c r="G108" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H108" s="2">
         <v>0</v>
@@ -4594,16 +4594,16 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B109" s="2">
-        <v>46021.30255787037</v>
+        <v>46021.29760416667</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D109" s="2">
-        <v>46021.54674768518</v>
+        <v>46021.59293981481</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>195</v>
@@ -4612,7 +4612,7 @@
         <v>206</v>
       </c>
       <c r="G109" s="2">
-        <v>18.35</v>
+        <v>19.25</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
@@ -4626,16 +4626,16 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B110" s="2">
-        <v>46021.5621875</v>
+        <v>46021.30344907408</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D110" s="2">
-        <v>46021.71854166667</v>
+        <v>46021.71900462963</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>195</v>
@@ -4658,16 +4658,16 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B111" s="2">
-        <v>46021.31924768518</v>
+        <v>46021.30381944445</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D111" s="2">
-        <v>46021.50954861111</v>
+        <v>46021.59515046296</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>195</v>
@@ -4676,7 +4676,7 @@
         <v>206</v>
       </c>
       <c r="G111" s="2">
-        <v>19.75</v>
+        <v>18.35</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4690,16 +4690,16 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B112" s="2">
-        <v>46021.546875</v>
+        <v>46021.52431712963</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D112" s="2">
-        <v>46021.72003472222</v>
+        <v>46021.71839120371</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>195</v>
@@ -4722,16 +4722,16 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B113" s="2">
-        <v>46021.30517361111</v>
+        <v>46021.30069444444</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D113" s="2">
-        <v>46021.56539351852</v>
+        <v>46021.51075231482</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>195</v>
@@ -4740,7 +4740,7 @@
         <v>206</v>
       </c>
       <c r="G113" s="2">
-        <v>17.85</v>
+        <v>18.35</v>
       </c>
       <c r="H113" s="2">
         <v>0</v>
@@ -4754,16 +4754,16 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B114" s="2">
-        <v>46021.60690972222</v>
+        <v>46021.55568287037</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D114" s="2">
-        <v>46021.71853009259</v>
+        <v>46021.71855324074</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>195</v>
@@ -4772,7 +4772,7 @@
         <v>206</v>
       </c>
       <c r="G114" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H114" s="2">
         <v>0</v>
@@ -4789,13 +4789,13 @@
         <v>101</v>
       </c>
       <c r="B115" s="2">
-        <v>46021.33921296296</v>
+        <v>46021.32858796296</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D115" s="2">
-        <v>46021.66471064815</v>
+        <v>46021.59804398148</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>195</v>
@@ -4804,7 +4804,7 @@
         <v>207</v>
       </c>
       <c r="G115" s="2">
-        <v>23.35</v>
+        <v>19.6</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4821,13 +4821,13 @@
         <v>102</v>
       </c>
       <c r="B116" s="2">
-        <v>46021.32858796296</v>
+        <v>46021.33921296296</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D116" s="2">
-        <v>46021.59804398148</v>
+        <v>46021.66471064815</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>195</v>
@@ -4836,7 +4836,7 @@
         <v>207</v>
       </c>
       <c r="G116" s="2">
-        <v>19.6</v>
+        <v>23.35</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -4885,18 +4885,22 @@
         <v>104</v>
       </c>
       <c r="B118" s="2">
-        <v>46021.31333333333</v>
+        <v>46021.31305555555</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
+      <c r="D118" s="2">
+        <v>46021.56645833333</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F118" s="2" t="s">
         <v>209</v>
       </c>
       <c r="G118" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -4910,16 +4914,16 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B119" s="2">
-        <v>46021.37400462963</v>
+        <v>46021.31170138889</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D119" s="2">
-        <v>46021.73636574074</v>
+        <v>46021.58542824074</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>195</v>
@@ -4928,7 +4932,7 @@
         <v>209</v>
       </c>
       <c r="G119" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -4942,16 +4946,16 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B120" s="2">
-        <v>46021.31305555555</v>
+        <v>46021.31333333333</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D120" s="2">
-        <v>46021.56645833333</v>
+        <v>46021.70833333334</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>195</v>
@@ -4960,7 +4964,7 @@
         <v>209</v>
       </c>
       <c r="G120" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
@@ -4974,16 +4978,16 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B121" s="2">
-        <v>46021.31453703704</v>
+        <v>46021.37400462963</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D121" s="2">
-        <v>46021.70487268519</v>
+        <v>46021.73636574074</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>195</v>
@@ -4992,7 +4996,7 @@
         <v>209</v>
       </c>
       <c r="G121" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H121" s="2">
         <v>0</v>
@@ -5006,16 +5010,16 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B122" s="2">
-        <v>46021.31170138889</v>
+        <v>46021.31453703704</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D122" s="2">
-        <v>46021.58542824074</v>
+        <v>46021.70487268519</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>195</v>
@@ -5073,25 +5077,25 @@
         <v>109</v>
       </c>
       <c r="B124" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.37578703704</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D124" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.68872685185</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G124" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H124" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I124" s="2">
         <v>0</v>
@@ -5105,28 +5109,28 @@
         <v>110</v>
       </c>
       <c r="B125" s="2">
-        <v>46021.38815972222</v>
+        <v>46021</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D125" s="2">
-        <v>46021.71732638889</v>
+        <v>46021</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G125" s="2">
-        <v>22.4</v>
+        <v>15.9</v>
       </c>
       <c r="H125" s="2">
         <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>244</v>
@@ -5137,13 +5141,13 @@
         <v>111</v>
       </c>
       <c r="B126" s="2">
-        <v>46021.24775462963</v>
+        <v>46021.36637731481</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D126" s="2">
-        <v>46021.70616898148</v>
+        <v>46021.68155092592</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>195</v>
@@ -5152,7 +5156,7 @@
         <v>211</v>
       </c>
       <c r="G126" s="2">
-        <v>22.4</v>
+        <v>18.35</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
@@ -5169,25 +5173,25 @@
         <v>112</v>
       </c>
       <c r="B127" s="2">
-        <v>46021.37578703704</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D127" s="2">
-        <v>46021.68872685185</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G127" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H127" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I127" s="2">
         <v>0</v>
@@ -5201,16 +5205,16 @@
         <v>113</v>
       </c>
       <c r="B128" s="2">
-        <v>46021.36637731481</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D128" s="2">
-        <v>46021.68155092592</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>211</v>
@@ -5219,7 +5223,7 @@
         <v>18.35</v>
       </c>
       <c r="H128" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I128" s="2">
         <v>0</v>
@@ -5233,13 +5237,13 @@
         <v>114</v>
       </c>
       <c r="B129" s="2">
-        <v>46021.36543981481</v>
+        <v>46021.37207175926</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D129" s="2">
-        <v>46021.74340277778</v>
+        <v>46021.62596064815</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>195</v>
@@ -5265,16 +5269,16 @@
         <v>115</v>
       </c>
       <c r="B130" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.36543981481</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D130" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.74340277778</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>211</v>
@@ -5283,7 +5287,7 @@
         <v>18.35</v>
       </c>
       <c r="H130" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I130" s="2">
         <v>0</v>
@@ -5297,25 +5301,25 @@
         <v>116</v>
       </c>
       <c r="B131" s="2">
-        <v>46021.31255787037</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D131" s="2">
-        <v>46021.62383101852</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G131" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H131" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I131" s="2">
         <v>0</v>
@@ -5329,28 +5333,28 @@
         <v>117</v>
       </c>
       <c r="B132" s="2">
-        <v>46021</v>
+        <v>46021.31255787037</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D132" s="2">
-        <v>46021</v>
+        <v>46021.62383101852</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G132" s="2">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
       </c>
       <c r="I132" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>244</v>
@@ -5358,7 +5362,7 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B133" s="2">
         <v>46021.37517361111</v>
@@ -5393,13 +5397,13 @@
         <v>118</v>
       </c>
       <c r="B134" s="2">
-        <v>46021.37207175926</v>
+        <v>46021.38815972222</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D134" s="2">
-        <v>46021.62596064815</v>
+        <v>46021.71732638889</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>195</v>
@@ -5408,7 +5412,7 @@
         <v>211</v>
       </c>
       <c r="G134" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H134" s="2">
         <v>0</v>
@@ -5425,25 +5429,25 @@
         <v>119</v>
       </c>
       <c r="B135" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.24775462963</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D135" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.70616898148</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G135" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H135" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I135" s="2">
         <v>0</v>
@@ -5457,13 +5461,13 @@
         <v>120</v>
       </c>
       <c r="B136" s="2">
-        <v>46021.33490740741</v>
+        <v>46021.45498842592</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D136" s="2">
-        <v>46021.68</v>
+        <v>46021.69689814815</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>195</v>
@@ -5489,16 +5493,16 @@
         <v>121</v>
       </c>
       <c r="B137" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.30840277778</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D137" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.62440972222</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>212</v>
@@ -5507,7 +5511,7 @@
         <v>18.35</v>
       </c>
       <c r="H137" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I137" s="2">
         <v>0</v>
@@ -5521,16 +5525,16 @@
         <v>122</v>
       </c>
       <c r="B138" s="2">
-        <v>46021.5277662037</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D138" s="2">
-        <v>46021.68055555555</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>212</v>
@@ -5539,7 +5543,7 @@
         <v>18.35</v>
       </c>
       <c r="H138" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I138" s="2">
         <v>0</v>
@@ -5550,19 +5554,19 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B139" s="2">
-        <v>46021.33628472222</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D139" s="2">
-        <v>46021.4570949074</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>212</v>
@@ -5571,7 +5575,7 @@
         <v>18.35</v>
       </c>
       <c r="H139" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I139" s="2">
         <v>0</v>
@@ -5582,16 +5586,16 @@
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B140" s="2">
-        <v>46021.45960648148</v>
+        <v>46021.33490740741</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D140" s="2">
-        <v>46021.69760416666</v>
+        <v>46021.68</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>195</v>
@@ -5614,16 +5618,16 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B141" s="2">
-        <v>46021.32020833333</v>
+        <v>46021.25960648148</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D141" s="2">
-        <v>46021.62804398148</v>
+        <v>46021.69722222222</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>195</v>
@@ -5632,7 +5636,7 @@
         <v>212</v>
       </c>
       <c r="G141" s="2">
-        <v>18.35</v>
+        <v>23.35</v>
       </c>
       <c r="H141" s="2">
         <v>0</v>
@@ -5646,16 +5650,16 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B142" s="2">
-        <v>46021.29318287037</v>
+        <v>46021.33418981481</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D142" s="2">
-        <v>46021.72958333333</v>
+        <v>46021.7685300926</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>195</v>
@@ -5664,7 +5668,7 @@
         <v>212</v>
       </c>
       <c r="G142" s="2">
-        <v>21.8</v>
+        <v>18.35</v>
       </c>
       <c r="H142" s="2">
         <v>0</v>
@@ -5678,16 +5682,16 @@
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B143" s="2">
-        <v>46021.33418981481</v>
+        <v>46021.37467592592</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D143" s="2">
-        <v>46021.7685300926</v>
+        <v>46021.69726851852</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>195</v>
@@ -5710,16 +5714,16 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B144" s="2">
-        <v>46021.25960648148</v>
+        <v>46021.2583912037</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D144" s="2">
-        <v>46021.69722222222</v>
+        <v>46021.69268518518</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>195</v>
@@ -5728,7 +5732,7 @@
         <v>212</v>
       </c>
       <c r="G144" s="2">
-        <v>23.35</v>
+        <v>18.35</v>
       </c>
       <c r="H144" s="2">
         <v>0</v>
@@ -5742,16 +5746,16 @@
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B145" s="2">
-        <v>46021.45045138889</v>
+        <v>46021.26021990741</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D145" s="2">
-        <v>46021.70125</v>
+        <v>46021.70833333334</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>195</v>
@@ -5760,7 +5764,7 @@
         <v>212</v>
       </c>
       <c r="G145" s="2">
-        <v>18.35</v>
+        <v>19.65</v>
       </c>
       <c r="H145" s="2">
         <v>0</v>
@@ -5774,16 +5778,16 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B146" s="2">
-        <v>46021.2583912037</v>
+        <v>46021.25751157408</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D146" s="2">
-        <v>46021.69268518518</v>
+        <v>46021.6255787037</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>195</v>
@@ -5809,13 +5813,13 @@
         <v>130</v>
       </c>
       <c r="B147" s="2">
-        <v>46021.37467592592</v>
+        <v>46021.63719907407</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D147" s="2">
-        <v>46021.69726851852</v>
+        <v>46021.69123842593</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>195</v>
@@ -5841,16 +5845,16 @@
         <v>131</v>
       </c>
       <c r="B148" s="2">
-        <v>46021.63719907407</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D148" s="2">
-        <v>46021.69123842593</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>212</v>
@@ -5859,7 +5863,7 @@
         <v>18.35</v>
       </c>
       <c r="H148" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
@@ -5902,16 +5906,16 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B150" s="2">
-        <v>46021.25751157408</v>
+        <v>46021.30881944444</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D150" s="2">
-        <v>46021.6255787037</v>
+        <v>46021.58832175926</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>195</v>
@@ -5920,7 +5924,7 @@
         <v>212</v>
       </c>
       <c r="G150" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H150" s="2">
         <v>0</v>
@@ -5934,28 +5938,28 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B151" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.30929398148</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D151" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.60993055555</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>212</v>
       </c>
       <c r="G151" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H151" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I151" s="2">
         <v>0</v>
@@ -5966,16 +5970,16 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B152" s="2">
-        <v>46021.30840277778</v>
+        <v>46021.29113425926</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D152" s="2">
-        <v>46021.62440972222</v>
+        <v>46021.61934027778</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>195</v>
@@ -5998,19 +6002,19 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B153" s="2">
-        <v>46021.29113425926</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D153" s="2">
-        <v>46021.61934027778</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>212</v>
@@ -6019,7 +6023,7 @@
         <v>18.35</v>
       </c>
       <c r="H153" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I153" s="2">
         <v>0</v>
@@ -6030,16 +6034,16 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B154" s="2">
-        <v>46021.45498842592</v>
+        <v>46021.29318287037</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D154" s="2">
-        <v>46021.69689814815</v>
+        <v>46021.72958333333</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>195</v>
@@ -6048,7 +6052,7 @@
         <v>212</v>
       </c>
       <c r="G154" s="2">
-        <v>18.35</v>
+        <v>21.8</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -6062,16 +6066,16 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B155" s="2">
-        <v>46021.26021990741</v>
+        <v>46021.45833333334</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D155" s="2">
-        <v>46021.70833333334</v>
+        <v>46021.6980787037</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>195</v>
@@ -6080,7 +6084,7 @@
         <v>212</v>
       </c>
       <c r="G155" s="2">
-        <v>19.65</v>
+        <v>18.35</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -6094,16 +6098,16 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B156" s="2">
-        <v>46021.45833333334</v>
+        <v>46021.32020833333</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D156" s="2">
-        <v>46021.6980787037</v>
+        <v>46021.62804398148</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>195</v>
@@ -6126,19 +6130,19 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B157" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.45045138889</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D157" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.70125</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>212</v>
@@ -6147,7 +6151,7 @@
         <v>18.35</v>
       </c>
       <c r="H157" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I157" s="2">
         <v>0</v>
@@ -6158,16 +6162,16 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B158" s="2">
-        <v>46021.30881944444</v>
+        <v>46021.33628472222</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D158" s="2">
-        <v>46021.58832175926</v>
+        <v>46021.4570949074</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>195</v>
@@ -6176,7 +6180,7 @@
         <v>212</v>
       </c>
       <c r="G158" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -6193,16 +6197,16 @@
         <v>141</v>
       </c>
       <c r="B159" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.5277662037</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D159" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.68055555555</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>212</v>
@@ -6211,7 +6215,7 @@
         <v>18.35</v>
       </c>
       <c r="H159" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I159" s="2">
         <v>0</v>
@@ -6225,13 +6229,13 @@
         <v>142</v>
       </c>
       <c r="B160" s="2">
-        <v>46021.30929398148</v>
+        <v>46021.45960648148</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D160" s="2">
-        <v>46021.60993055555</v>
+        <v>46021.69760416666</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>195</v>
@@ -6240,7 +6244,7 @@
         <v>212</v>
       </c>
       <c r="G160" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -6289,16 +6293,16 @@
         <v>144</v>
       </c>
       <c r="B162" s="2">
-        <v>46021</v>
+        <v>46021.54820601852</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D162" s="2">
-        <v>46021</v>
+        <v>46021.91363425926</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>213</v>
@@ -6310,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="I162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>246</v>
@@ -6321,16 +6325,16 @@
         <v>144</v>
       </c>
       <c r="B163" s="2">
-        <v>46021.54820601852</v>
+        <v>46021</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D163" s="2">
-        <v>46021.91363425926</v>
+        <v>46021</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>213</v>
@@ -6342,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>246</v>
@@ -6353,13 +6357,13 @@
         <v>145</v>
       </c>
       <c r="B164" s="2">
-        <v>46021.37381944444</v>
+        <v>46021.38155092593</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D164" s="2">
-        <v>46021.70540509259</v>
+        <v>46021.70805555556</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>195</v>
@@ -6368,7 +6372,7 @@
         <v>214</v>
       </c>
       <c r="G164" s="2">
-        <v>18.35</v>
+        <v>23.35</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -6385,13 +6389,13 @@
         <v>146</v>
       </c>
       <c r="B165" s="2">
-        <v>46021.37594907408</v>
+        <v>46021.40958333333</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D165" s="2">
-        <v>46021.738125</v>
+        <v>46021.7144675926</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>195</v>
@@ -6400,7 +6404,7 @@
         <v>214</v>
       </c>
       <c r="G165" s="2">
-        <v>20.7</v>
+        <v>18.35</v>
       </c>
       <c r="H165" s="2">
         <v>0</v>
@@ -6417,13 +6421,13 @@
         <v>147</v>
       </c>
       <c r="B166" s="2">
-        <v>46021.40958333333</v>
+        <v>46021.45320601852</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D166" s="2">
-        <v>46021.7144675926</v>
+        <v>46021.63791666667</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>195</v>
@@ -6449,13 +6453,13 @@
         <v>148</v>
       </c>
       <c r="B167" s="2">
-        <v>46021.38155092593</v>
+        <v>46021.37407407408</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D167" s="2">
-        <v>46021.70805555556</v>
+        <v>46021.71753472222</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>195</v>
@@ -6464,7 +6468,7 @@
         <v>214</v>
       </c>
       <c r="G167" s="2">
-        <v>23.35</v>
+        <v>18.35</v>
       </c>
       <c r="H167" s="2">
         <v>0</v>
@@ -6481,13 +6485,13 @@
         <v>149</v>
       </c>
       <c r="B168" s="2">
-        <v>46021.37407407408</v>
+        <v>46021.37594907408</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D168" s="2">
-        <v>46021.71753472222</v>
+        <v>46021.738125</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>195</v>
@@ -6496,7 +6500,7 @@
         <v>214</v>
       </c>
       <c r="G168" s="2">
-        <v>18.35</v>
+        <v>20.7</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6513,13 +6517,13 @@
         <v>150</v>
       </c>
       <c r="B169" s="2">
-        <v>46021.45320601852</v>
+        <v>46021.37381944444</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D169" s="2">
-        <v>46021.63791666667</v>
+        <v>46021.70540509259</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>195</v>
@@ -6545,13 +6549,13 @@
         <v>151</v>
       </c>
       <c r="B170" s="2">
-        <v>46021.62211805556</v>
+        <v>46021.2680787037</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D170" s="2">
-        <v>46021.92039351852</v>
+        <v>46021.50177083333</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>195</v>
@@ -6560,7 +6564,7 @@
         <v>215</v>
       </c>
       <c r="G170" s="2">
-        <v>18.35</v>
+        <v>17.85</v>
       </c>
       <c r="H170" s="2">
         <v>0</v>
@@ -6577,13 +6581,13 @@
         <v>152</v>
       </c>
       <c r="B171" s="2">
-        <v>46021.2680787037</v>
+        <v>46021.62211805556</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D171" s="2">
-        <v>46021.50177083333</v>
+        <v>46021.92039351852</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>195</v>
@@ -6592,7 +6596,7 @@
         <v>215</v>
       </c>
       <c r="G171" s="2">
-        <v>17.85</v>
+        <v>18.35</v>
       </c>
       <c r="H171" s="2">
         <v>0</v>
@@ -6609,13 +6613,13 @@
         <v>153</v>
       </c>
       <c r="B172" s="2">
-        <v>46021.68135416666</v>
+        <v>46021.37393518518</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D172" s="2">
-        <v>46021.99353009259</v>
+        <v>46021.58640046296</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>195</v>
@@ -6624,7 +6628,7 @@
         <v>216</v>
       </c>
       <c r="G172" s="2">
-        <v>22.4</v>
+        <v>20.2</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6641,13 +6645,13 @@
         <v>154</v>
       </c>
       <c r="B173" s="2">
-        <v>46021.37541666667</v>
+        <v>46021.68135416666</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D173" s="2">
-        <v>46021.68751157408</v>
+        <v>46021.99353009259</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>195</v>
@@ -6656,7 +6660,7 @@
         <v>216</v>
       </c>
       <c r="G173" s="2">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H173" s="2">
         <v>0</v>
@@ -6673,13 +6677,13 @@
         <v>155</v>
       </c>
       <c r="B174" s="2">
-        <v>46021.37393518518</v>
+        <v>46021.37541666667</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D174" s="2">
-        <v>46021.58640046296</v>
+        <v>46021.68751157408</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>195</v>
@@ -6688,7 +6692,7 @@
         <v>216</v>
       </c>
       <c r="G174" s="2">
-        <v>20.2</v>
+        <v>23</v>
       </c>
       <c r="H174" s="2">
         <v>0</v>
@@ -6705,13 +6709,13 @@
         <v>156</v>
       </c>
       <c r="B175" s="2">
-        <v>46021.34148148148</v>
+        <v>46021.31547453703</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D175" s="2">
-        <v>46021.50724537037</v>
+        <v>46021.53782407408</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>195</v>
@@ -6720,7 +6724,7 @@
         <v>217</v>
       </c>
       <c r="G175" s="2">
-        <v>23.85</v>
+        <v>19.25</v>
       </c>
       <c r="H175" s="2">
         <v>0</v>
@@ -6865,25 +6869,25 @@
         <v>161</v>
       </c>
       <c r="B180" s="2">
-        <v>46021.5</v>
+        <v>46021.34148148148</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D180" s="2">
-        <v>46021.5</v>
+        <v>46021.50724537037</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>217</v>
       </c>
       <c r="G180" s="2">
-        <v>19.6</v>
+        <v>23.85</v>
       </c>
       <c r="H180" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I180" s="2">
         <v>0</v>
@@ -6897,25 +6901,25 @@
         <v>162</v>
       </c>
       <c r="B181" s="2">
-        <v>46021.31547453703</v>
+        <v>46021.5</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D181" s="2">
-        <v>46021.53782407408</v>
+        <v>46021.5</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>217</v>
       </c>
       <c r="G181" s="2">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="H181" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I181" s="2">
         <v>0</v>
@@ -6993,13 +6997,13 @@
         <v>165</v>
       </c>
       <c r="B184" s="2">
-        <v>46021.69841435185</v>
+        <v>46021.575</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D184" s="2">
-        <v>46021.99342592592</v>
+        <v>46021.69486111111</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>195</v>
@@ -7008,7 +7012,7 @@
         <v>219</v>
       </c>
       <c r="G184" s="2">
-        <v>19.65</v>
+        <v>20.7</v>
       </c>
       <c r="H184" s="2">
         <v>0</v>
@@ -7025,13 +7029,13 @@
         <v>166</v>
       </c>
       <c r="B185" s="2">
-        <v>46021.56255787037</v>
+        <v>46021.37247685185</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D185" s="2">
-        <v>46021.86011574074</v>
+        <v>46021.59961805555</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>195</v>
@@ -7040,7 +7044,7 @@
         <v>219</v>
       </c>
       <c r="G185" s="2">
-        <v>24.8</v>
+        <v>20.7</v>
       </c>
       <c r="H185" s="2">
         <v>0</v>
@@ -7057,13 +7061,13 @@
         <v>166</v>
       </c>
       <c r="B186" s="2">
-        <v>46021.40107638889</v>
+        <v>46021.61828703704</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D186" s="2">
-        <v>46021.53712962963</v>
+        <v>46021.68643518518</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>195</v>
@@ -7072,7 +7076,7 @@
         <v>219</v>
       </c>
       <c r="G186" s="2">
-        <v>24.8</v>
+        <v>20.7</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -7089,13 +7093,13 @@
         <v>167</v>
       </c>
       <c r="B187" s="2">
-        <v>46021.6838425926</v>
+        <v>46021.37746527778</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D187" s="2">
-        <v>46021.99325231482</v>
+        <v>46021.63792824074</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>195</v>
@@ -7104,7 +7108,7 @@
         <v>219</v>
       </c>
       <c r="G187" s="2">
-        <v>20.7</v>
+        <v>21.45</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
@@ -7121,13 +7125,13 @@
         <v>168</v>
       </c>
       <c r="B188" s="2">
-        <v>46021.37746527778</v>
+        <v>46021.6838425926</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D188" s="2">
-        <v>46021.63792824074</v>
+        <v>46021.99325231482</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>195</v>
@@ -7136,7 +7140,7 @@
         <v>219</v>
       </c>
       <c r="G188" s="2">
-        <v>21.45</v>
+        <v>20.7</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -7150,16 +7154,16 @@
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B189" s="2">
-        <v>46021.61828703704</v>
+        <v>46021.53320601852</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D189" s="2">
-        <v>46021.68643518518</v>
+        <v>46021.69238425926</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>195</v>
@@ -7168,7 +7172,7 @@
         <v>219</v>
       </c>
       <c r="G189" s="2">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -7182,16 +7186,16 @@
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B190" s="2">
-        <v>46021.37001157407</v>
+        <v>46021.40107638889</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D190" s="2">
-        <v>46021.55858796297</v>
+        <v>46021.53712962963</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>195</v>
@@ -7200,7 +7204,7 @@
         <v>219</v>
       </c>
       <c r="G190" s="2">
-        <v>20.7</v>
+        <v>24.8</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -7217,13 +7221,13 @@
         <v>170</v>
       </c>
       <c r="B191" s="2">
-        <v>46021.575</v>
+        <v>46021.69841435185</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D191" s="2">
-        <v>46021.69486111111</v>
+        <v>46021.99342592592</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>195</v>
@@ -7232,7 +7236,7 @@
         <v>219</v>
       </c>
       <c r="G191" s="2">
-        <v>20.7</v>
+        <v>19.65</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -7246,16 +7250,16 @@
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B192" s="2">
-        <v>46021.53320601852</v>
+        <v>46021.37001157407</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D192" s="2">
-        <v>46021.69238425926</v>
+        <v>46021.55858796297</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>195</v>
@@ -7264,7 +7268,7 @@
         <v>219</v>
       </c>
       <c r="G192" s="2">
-        <v>21.2</v>
+        <v>20.7</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -7281,13 +7285,13 @@
         <v>169</v>
       </c>
       <c r="B193" s="2">
-        <v>46021.37247685185</v>
+        <v>46021.56255787037</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D193" s="2">
-        <v>46021.59961805555</v>
+        <v>46021.86011574074</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>195</v>
@@ -7296,7 +7300,7 @@
         <v>219</v>
       </c>
       <c r="G193" s="2">
-        <v>20.7</v>
+        <v>24.8</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -7313,13 +7317,13 @@
         <v>171</v>
       </c>
       <c r="B194" s="2">
-        <v>46021.31934027778</v>
+        <v>46021.37978009259</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D194" s="2">
-        <v>46021.6910300926</v>
+        <v>46021.68116898148</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>195</v>
@@ -7328,7 +7332,7 @@
         <v>220</v>
       </c>
       <c r="G194" s="2">
-        <v>26.45</v>
+        <v>26.8</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -7345,25 +7349,25 @@
         <v>172</v>
       </c>
       <c r="B195" s="2">
-        <v>46021.32467592593</v>
+        <v>46021.5</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D195" s="2">
-        <v>46021.60603009259</v>
+        <v>46021.5</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>220</v>
       </c>
       <c r="G195" s="2">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="H195" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I195" s="2">
         <v>0</v>
@@ -7377,25 +7381,25 @@
         <v>173</v>
       </c>
       <c r="B196" s="2">
-        <v>46021.5</v>
+        <v>46021.32467592593</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D196" s="2">
-        <v>46021.5</v>
+        <v>46021.60603009259</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>220</v>
       </c>
       <c r="G196" s="2">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="H196" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I196" s="2">
         <v>0</v>
@@ -7441,13 +7445,13 @@
         <v>175</v>
       </c>
       <c r="B198" s="2">
-        <v>46021.37978009259</v>
+        <v>46021.31934027778</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D198" s="2">
-        <v>46021.68116898148</v>
+        <v>46021.6910300926</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>195</v>
@@ -7456,7 +7460,7 @@
         <v>220</v>
       </c>
       <c r="G198" s="2">
-        <v>26.8</v>
+        <v>26.45</v>
       </c>
       <c r="H198" s="2">
         <v>0</v>
@@ -7505,13 +7509,13 @@
         <v>177</v>
       </c>
       <c r="B200" s="2">
-        <v>46021.36476851852</v>
+        <v>46021.35438657407</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D200" s="2">
-        <v>46021.71784722222</v>
+        <v>46021.72703703704</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>195</v>
@@ -7520,7 +7524,7 @@
         <v>222</v>
       </c>
       <c r="G200" s="2">
-        <v>30.78</v>
+        <v>31.64</v>
       </c>
       <c r="H200" s="2">
         <v>0</v>
@@ -7537,25 +7541,25 @@
         <v>178</v>
       </c>
       <c r="B201" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.32997685186</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D201" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.73337962963</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G201" s="2">
-        <v>30.78</v>
+        <v>31.64</v>
       </c>
       <c r="H201" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I201" s="2">
         <v>0</v>
@@ -7569,25 +7573,25 @@
         <v>179</v>
       </c>
       <c r="B202" s="2">
-        <v>46021.35438657407</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D202" s="2">
-        <v>46021.72703703704</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G202" s="2">
-        <v>31.64</v>
+        <v>30.78</v>
       </c>
       <c r="H202" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I202" s="2">
         <v>0</v>
@@ -7633,13 +7637,13 @@
         <v>181</v>
       </c>
       <c r="B204" s="2">
-        <v>46021.32997685186</v>
+        <v>46021.36476851852</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D204" s="2">
-        <v>46021.73337962963</v>
+        <v>46021.71784722222</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>195</v>
@@ -7648,7 +7652,7 @@
         <v>222</v>
       </c>
       <c r="G204" s="2">
-        <v>31.64</v>
+        <v>30.78</v>
       </c>
       <c r="H204" s="2">
         <v>0</v>
@@ -7665,25 +7669,25 @@
         <v>182</v>
       </c>
       <c r="B205" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.37658564815</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D205" s="2">
-        <v>46021.33333333334</v>
+        <v>46021.75953703704</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>223</v>
       </c>
       <c r="G205" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H205" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I205" s="2">
         <v>0</v>
@@ -7697,25 +7701,25 @@
         <v>183</v>
       </c>
       <c r="B206" s="2">
-        <v>46021.37658564815</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D206" s="2">
-        <v>46021.75953703704</v>
+        <v>46021.33333333334</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>223</v>
       </c>
       <c r="G206" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H206" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I206" s="2">
         <v>0</v>
@@ -7761,13 +7765,13 @@
         <v>185</v>
       </c>
       <c r="B208" s="2">
-        <v>46021.29733796296</v>
+        <v>46021.48813657407</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D208" s="2">
-        <v>46021.534375</v>
+        <v>46021.52363425926</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>195</v>
@@ -7776,7 +7780,7 @@
         <v>224</v>
       </c>
       <c r="G208" s="2">
-        <v>26.75</v>
+        <v>23</v>
       </c>
       <c r="H208" s="2">
         <v>0</v>
@@ -7790,7 +7794,7 @@
     </row>
     <row r="209" spans="1:10">
       <c r="A209" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B209" s="2">
         <v>46021.56311342592</v>
@@ -7825,13 +7829,13 @@
         <v>186</v>
       </c>
       <c r="B210" s="2">
-        <v>46021.48813657407</v>
+        <v>46021.29733796296</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D210" s="2">
-        <v>46021.52363425926</v>
+        <v>46021.534375</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>195</v>
@@ -7840,7 +7844,7 @@
         <v>224</v>
       </c>
       <c r="G210" s="2">
-        <v>23</v>
+        <v>26.75</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -7854,7 +7858,7 @@
     </row>
     <row r="211" spans="1:10">
       <c r="A211" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B211" s="2">
         <v>46021.57773148148</v>
@@ -7889,13 +7893,13 @@
         <v>187</v>
       </c>
       <c r="B212" s="2">
-        <v>46021.33849537037</v>
+        <v>46021.34313657408</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D212" s="2">
-        <v>46021.67280092592</v>
+        <v>46021.53428240741</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>195</v>
@@ -7904,7 +7908,7 @@
         <v>225</v>
       </c>
       <c r="G212" s="2">
-        <v>20.2</v>
+        <v>28.4</v>
       </c>
       <c r="H212" s="2">
         <v>0</v>
@@ -7918,16 +7922,16 @@
     </row>
     <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B213" s="2">
-        <v>46021.34313657408</v>
+        <v>46021.57827546296</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D213" s="2">
-        <v>46021.53428240741</v>
+        <v>46021.64050925926</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>195</v>
@@ -7953,13 +7957,13 @@
         <v>188</v>
       </c>
       <c r="B214" s="2">
-        <v>46021.57827546296</v>
+        <v>46021.33849537037</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D214" s="2">
-        <v>46021.64050925926</v>
+        <v>46021.67280092592</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>195</v>
@@ -7968,7 +7972,7 @@
         <v>225</v>
       </c>
       <c r="G214" s="2">
-        <v>28.4</v>
+        <v>20.2</v>
       </c>
       <c r="H214" s="2">
         <v>0</v>
